--- a/results/Int All Data -0.6/Rando_8_permute.xlsx
+++ b/results/Int All Data -0.6/Rando_8_permute.xlsx
@@ -440,117 +440,117 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.7059030165117635</v>
+        <v>0.6990334109303616</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>accy_skewness</t>
+          <t>accx_iqr</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.7064169368602171</v>
+        <v>0.7028632954422507</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>scr_n_below_mean</t>
+          <t>scl_max</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.7066931799541398</v>
+        <v>0.7046395926330522</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>scr_sum</t>
+          <t>scr_n_sign_changes</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.7088645588661294</v>
+        <v>0.7046395926330522</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>bvp_max</t>
+          <t>accz_perm_entropy</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.7094566579297299</v>
+        <v>0.7059009224390362</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>accz_mean</t>
+          <t>scr_n_above_mean</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.7022649141604689</v>
+        <v>0.7059801481905467</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>scl_n_sign_changes</t>
+          <t>accz_pct_5</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.7025411572543915</v>
+        <v>0.7019115393877629</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>accz_entropy</t>
+          <t>scl_perm_entropy</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.7070402725086642</v>
+        <v>0.7025432513271186</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>hrv_iqr</t>
+          <t>accz_entropy</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.7020689438544201</v>
+        <v>0.7049898262966673</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>hrv_entropy</t>
+          <t>accx_ptp</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.6998569050303117</v>
+        <v>0.7059363471693372</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>bvp_pct_95</t>
+          <t>scr_mean</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.6960280675547862</v>
+        <v>0.7081452448843548</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>bvp_skewness</t>
+          <t>accx_iqr_5_95</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.698276578145559</v>
+        <v>0.7077512101995302</v>
       </c>
     </row>
     <row r="14">
@@ -560,1427 +560,1427 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.698276578145559</v>
+        <v>0.7077512101995302</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>accx_kurtosis</t>
+          <t>hrv_lineintegral</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.697921109300126</v>
+        <v>0.7048324218300102</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>hrv_svd_entropy</t>
+          <t>accy_energy</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.6957497303881364</v>
+        <v>0.7017947948332246</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>accy_iqr_5_95</t>
+          <t>accz_peaks</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.6974478488637911</v>
+        <v>0.7033719806088865</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>scl_pct_95</t>
+          <t>accz_mean</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.695395308579067</v>
+        <v>0.6839004198615818</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>accy_pct_5</t>
+          <t>accz_pct_95</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.6965357056850585</v>
+        <v>0.6709044300108542</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>accz_iqr</t>
+          <t>bvp_iqr_5_95</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.6936158702791748</v>
+        <v>0.6703915566987642</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>accy_std</t>
+          <t>accy_mean</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.7007992377575274</v>
+        <v>0.691315182376284</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>accz_ptp</t>
+          <t>accy_entropy</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.69882487618795</v>
+        <v>0.6837346391040161</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>bvp_ptp</t>
+          <t>accy_iqr</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.6945206842033624</v>
+        <v>0.6853149659887687</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>accz_n_sign_changes</t>
+          <t>scr_iqr_5_95</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.6928236127640712</v>
+        <v>0.6842881723282249</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>scl_n_below_mean</t>
+          <t>bvp_perm_entropy</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.6915205760096048</v>
+        <v>0.6815674483374807</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
         <is>
-          <t>hrv_pct_95</t>
+          <t>hrv_rms</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.6963783012184013</v>
+        <v>0.6809357363981251</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
         <is>
-          <t>accx_pct_95</t>
+          <t>hrv_mean</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.6984704543788806</v>
+        <v>0.678172258422535</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>scr_energy</t>
+          <t>bvp_lineintegral</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.6970881918729037</v>
+        <v>0.6791187792952049</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_sign_changes</t>
+          <t>scr_ptp</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.7008378035969189</v>
+        <v>0.6749323789015192</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="inlineStr">
         <is>
-          <t>accz_max</t>
+          <t>accz_ptp</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.69301958307012</v>
+        <v>0.674892766025764</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="inlineStr">
         <is>
-          <t>hrv_peaks</t>
+          <t>accx_rms</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0.6930591959458752</v>
+        <v>0.6811327537405374</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="inlineStr">
         <is>
-          <t>accz_peaks</t>
+          <t>bvp_sum</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>0.6986611895031114</v>
+        <v>0.6814089968344601</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="inlineStr">
         <is>
-          <t>accz_energy</t>
+          <t>accz_kurtosis</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0.7005135713363325</v>
+        <v>0.6835803757464496</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>accz_sum</t>
+          <t>scr_lineintegral</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>0.7106521989508696</v>
+        <v>0.6863438537220398</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="inlineStr">
         <is>
-          <t>bvp_kurtosis</t>
+          <t>scl_skewness</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>0.7115601539841478</v>
+        <v>0.6863042408462846</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="inlineStr">
         <is>
-          <t>hrv_mean</t>
+          <t>accx_n_sign_changes</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>0.685975820440244</v>
+        <v>0.6855536902796634</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="inlineStr">
         <is>
-          <t>bvp_mean</t>
+          <t>bvp_ptp</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>0.685975820440244</v>
+        <v>0.6879231335704289</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="inlineStr">
         <is>
-          <t>scl_sum</t>
+          <t>accz_skewness</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>0.6695106501048782</v>
+        <v>0.6841724748100502</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="inlineStr">
         <is>
-          <t>bvp_pct_5</t>
+          <t>hrv_max</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>0.6796190881709322</v>
+        <v>0.6855964442645093</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_sign_changes</t>
+          <t>scr_pct_95</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>0.6796190881709322</v>
+        <v>0.6808971705587334</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="inlineStr">
         <is>
-          <t>accy_max</t>
+          <t>scr_kurtosis</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>0.677061003828663</v>
+        <v>0.6825150162465142</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="1" t="inlineStr">
         <is>
-          <t>scl_lineintegral</t>
+          <t>hrv_sum</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>0.6721240528683561</v>
+        <v>0.6929393102822461</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="1" t="inlineStr">
         <is>
-          <t>bvp_entropy</t>
+          <t>hrv_pct_5</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>0.6721240528683561</v>
+        <v>0.6774623677680326</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="1" t="inlineStr">
         <is>
-          <t>bvp_std</t>
+          <t>accy_peaks</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>0.6605176547781504</v>
+        <v>0.6713818785926435</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_below_mean</t>
+          <t>bvp_max</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>0.6557016365178363</v>
+        <v>0.6602873067781644</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="1" t="inlineStr">
         <is>
-          <t>hrv_sum</t>
+          <t>accx_energy</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>0.6532550615482875</v>
+        <v>0.6605270781054227</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="1" t="inlineStr">
         <is>
-          <t>bvp_iqr</t>
+          <t>scr_n_below_mean</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>0.6647457621203184</v>
+        <v>0.6547228320239562</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="1" t="inlineStr">
         <is>
-          <t>accz_pct_5</t>
+          <t>bvp_n_above_mean</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>0.6051636343330205</v>
+        <v>0.6610399514175127</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="1" t="inlineStr">
         <is>
-          <t>accz_svd_entropy</t>
+          <t>accy_svd_entropy</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>0.6135249177203924</v>
+        <v>0.6705938092229943</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="1" t="inlineStr">
         <is>
-          <t>accy_pct_95</t>
+          <t>accz_n_below_mean</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>0.6287038038831089</v>
+        <v>0.6626213253386291</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="1" t="inlineStr">
         <is>
-          <t>accy_n_above_mean</t>
+          <t>accz_max</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>0.634704020270624</v>
+        <v>0.6444892731124552</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="1" t="inlineStr">
         <is>
-          <t>scl_kurtosis</t>
+          <t>hrv_svd_entropy</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>0.6346644073948688</v>
+        <v>0.6453169553578596</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="1" t="inlineStr">
         <is>
-          <t>scr_iqr</t>
+          <t>scl_lineintegral</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>0.6265324249711193</v>
+        <v>0.6645831224718435</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="1" t="inlineStr">
         <is>
-          <t>scr_n_above_mean</t>
+          <t>scr_peaks</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>0.626808668065042</v>
+        <v>0.6604769948660316</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="1" t="inlineStr">
         <is>
-          <t>scl_energy</t>
+          <t>scr_svd_entropy</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>0.6140566376870269</v>
+        <v>0.658266003078287</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="1" t="inlineStr">
         <is>
-          <t>accx_mean</t>
+          <t>accy_rms</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>0.6174143087989445</v>
+        <v>0.6357610034796508</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="1" t="inlineStr">
         <is>
-          <t>accx_perm_entropy</t>
+          <t>hrv_iqr_5_95</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>0.6184431965322156</v>
+        <v>0.6356421648523853</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="1" t="inlineStr">
         <is>
-          <t>accy_rms</t>
+          <t>accz_svd_entropy</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>0.5923042827277392</v>
+        <v>0.6190581558897541</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="1" t="inlineStr">
         <is>
-          <t>scl_skewness</t>
+          <t>accy_perm_entropy</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>0.5923042827277392</v>
+        <v>0.6111252848811439</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="1" t="inlineStr">
         <is>
-          <t>hrv_rms</t>
+          <t>hrv_peaks</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>0.57169441894717</v>
+        <v>0.6105331858175435</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="1" t="inlineStr">
         <is>
-          <t>bvp_lineintegral</t>
+          <t>hrv_pct_95</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>0.5780438219619368</v>
+        <v>0.6001870704969584</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="1" t="inlineStr">
         <is>
-          <t>accx_std</t>
+          <t>hrv_entropy</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>0.5668763066141287</v>
+        <v>0.5984493391455485</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="1" t="inlineStr">
         <is>
-          <t>hrv_skewness</t>
+          <t>accz_min</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>0.5646663618627474</v>
+        <v>0.602158290957445</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="1" t="inlineStr">
         <is>
-          <t>hrv_pct_5</t>
+          <t>accy_max</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>0.5644662034112444</v>
+        <v>0.5893354111188281</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="1" t="inlineStr">
         <is>
-          <t>hrv_lineintegral</t>
+          <t>accx_peaks</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>0.537628916352265</v>
+        <v>0.5993302457394345</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="1" t="inlineStr">
         <is>
-          <t>scr_std</t>
+          <t>accz_iqr_5_95</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>0.5104632088872447</v>
+        <v>0.5976581286668086</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="1" t="inlineStr">
         <is>
-          <t>accy_mean</t>
+          <t>bvp_n_sign_changes</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>0.5191851963018675</v>
+        <v>0.5985254237879681</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="1" t="inlineStr">
         <is>
-          <t>scl_perm_entropy</t>
+          <t>scl_entropy</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>0.5186327101140222</v>
+        <v>0.5919653919580627</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="1" t="inlineStr">
         <is>
-          <t>accz_lineintegral</t>
+          <t>accz_iqr</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>0.506011908293575</v>
+        <v>0.6024240636877319</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="1" t="inlineStr">
         <is>
-          <t>scr_min</t>
+          <t>accx_entropy</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>0.506011908293575</v>
+        <v>0.6008458308757063</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="1" t="inlineStr">
         <is>
-          <t>scl_svd_entropy</t>
+          <t>accx_mean</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>0.5156491799960212</v>
+        <v>0.605269908523923</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="1" t="inlineStr">
         <is>
-          <t>scl_rms</t>
+          <t>scr_perm_entropy</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>0.5164341082565798</v>
+        <v>0.605269908523923</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="1" t="inlineStr">
         <is>
-          <t>scr_ptp</t>
+          <t>scr_iqr</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>0.5182489712867728</v>
+        <v>0.604957193663336</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="1" t="inlineStr">
         <is>
-          <t>accy_n_below_mean</t>
+          <t>accz_lineintegral</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>0.517852842529221</v>
+        <v>0.5938605277761296</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="1" t="inlineStr">
         <is>
-          <t>hrv_max</t>
+          <t>scl_min</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>0.5105183528023929</v>
+        <v>0.599271786209135</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="1" t="inlineStr">
         <is>
-          <t>accx_iqr_5_95</t>
+          <t>accx_pct_95</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>0.5186826188473526</v>
+        <v>0.5967095137214116</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="1" t="inlineStr">
         <is>
-          <t>hrv_energy</t>
+          <t>accz_rms</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>0.5170679142686625</v>
+        <v>0.56585980881116</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="1" t="inlineStr">
         <is>
-          <t>bvp_perm_entropy</t>
+          <t>hrv_min</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>0.5253719596681593</v>
+        <v>0.5990653455394506</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="1" t="inlineStr">
         <is>
-          <t>accx_n_above_mean</t>
+          <t>bvp_pct_5</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>0.52051632853209</v>
+        <v>0.582647117334385</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="1" t="inlineStr">
         <is>
-          <t>hrv_min</t>
+          <t>accy_n_sign_changes</t>
         </is>
       </c>
       <c r="B80" t="n">
-        <v>0.5182334402473798</v>
+        <v>0.585290709646346</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="1" t="inlineStr">
         <is>
-          <t>bvp_svd_entropy</t>
+          <t>accx_kurtosis</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>0.5150342206384828</v>
+        <v>0.5811460162011426</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="1" t="inlineStr">
         <is>
-          <t>accy_ptp</t>
+          <t>accx_lineintegral</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>0.5177559916655905</v>
+        <v>0.5953188749245262</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="1" t="inlineStr">
         <is>
-          <t>scr_mean</t>
+          <t>scr_std</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>0.513446564499185</v>
+        <v>0.5944484386942759</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="1" t="inlineStr">
         <is>
-          <t>accx_max</t>
+          <t>bvp_energy</t>
         </is>
       </c>
       <c r="B84" t="n">
-        <v>0.5065832411359646</v>
+        <v>0.5696542685927483</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="1" t="inlineStr">
         <is>
-          <t>scl_iqr_5_95</t>
+          <t>scl_n_above_mean</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>0.4952478509578637</v>
+        <v>0.5705997424290545</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="1" t="inlineStr">
         <is>
-          <t>scr_iqr_5_95</t>
+          <t>bvp_mean</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>0.4987847397940131</v>
+        <v>0.5705997424290545</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="1" t="inlineStr">
         <is>
-          <t>scl_ptp</t>
+          <t>bvp_skewness</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>0.4899022068036423</v>
+        <v>0.5691361600988403</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="1" t="inlineStr">
         <is>
-          <t>bvp_iqr_5_95</t>
+          <t>accy_lineintegral</t>
         </is>
       </c>
       <c r="B88" t="n">
-        <v>0.4901002711824182</v>
+        <v>0.5732808535440436</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="1" t="inlineStr">
         <is>
-          <t>bvp_energy</t>
+          <t>scl_iqr</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>0.4831952408707154</v>
+        <v>0.5776621772074144</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="1" t="inlineStr">
         <is>
-          <t>scl_iqr</t>
+          <t>accx_std</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>0.469895959486673</v>
+        <v>0.5745943606621458</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="1" t="inlineStr">
         <is>
-          <t>accx_ptp</t>
+          <t>scl_rms</t>
         </is>
       </c>
       <c r="B91" t="n">
-        <v>0.4714398146047613</v>
+        <v>0.5678050278686179</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="1" t="inlineStr">
         <is>
-          <t>bvp_sum</t>
+          <t>scl_ptp</t>
         </is>
       </c>
       <c r="B92" t="n">
-        <v>0.4711635715108385</v>
+        <v>0.5645672424203293</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="1" t="inlineStr">
         <is>
-          <t>accy_lineintegral</t>
+          <t>hrv_std</t>
         </is>
       </c>
       <c r="B93" t="n">
-        <v>0.4740813128439951</v>
+        <v>0.5578967482540669</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="1" t="inlineStr">
         <is>
-          <t>accy_entropy</t>
+          <t>accx_sum</t>
         </is>
       </c>
       <c r="B94" t="n">
-        <v>0.4756605926923842</v>
+        <v>0.5584200919297927</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="1" t="inlineStr">
         <is>
-          <t>accy_min</t>
+          <t>hrv_iqr</t>
         </is>
       </c>
       <c r="B95" t="n">
-        <v>0.497287826806225</v>
+        <v>0.5450082541366662</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="1" t="inlineStr">
         <is>
-          <t>scl_max</t>
+          <t>hrv_ptp</t>
         </is>
       </c>
       <c r="B96" t="n">
-        <v>0.4818098372556479</v>
+        <v>0.532063394561693</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="1" t="inlineStr">
         <is>
-          <t>accx_n_below_mean</t>
+          <t>scr_sum</t>
         </is>
       </c>
       <c r="B97" t="n">
-        <v>0.483269231440408</v>
+        <v>0.5309980350617577</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="1" t="inlineStr">
         <is>
-          <t>accx_peaks</t>
+          <t>hrv_n_sign_changes</t>
         </is>
       </c>
       <c r="B98" t="n">
-        <v>0.4723612066047054</v>
+        <v>0.5309980350617577</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="1" t="inlineStr">
         <is>
-          <t>accz_min</t>
+          <t>accy_n_above_mean</t>
         </is>
       </c>
       <c r="B99" t="n">
-        <v>0.469600869738206</v>
+        <v>0.5165520743535423</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="1" t="inlineStr">
         <is>
-          <t>accy_sum</t>
+          <t>hrv_kurtosis</t>
         </is>
       </c>
       <c r="B100" t="n">
-        <v>0.4373961252674305</v>
+        <v>0.5165520743535423</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="1" t="inlineStr">
         <is>
-          <t>scr_pct_5</t>
+          <t>scl_energy</t>
         </is>
       </c>
       <c r="B101" t="n">
-        <v>0.436921817794732</v>
+        <v>0.5203809118290679</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="1" t="inlineStr">
         <is>
-          <t>hrv_kurtosis</t>
+          <t>hrv_energy</t>
         </is>
       </c>
       <c r="B102" t="n">
-        <v>0.436921817794732</v>
+        <v>0.5299764765830317</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="1" t="inlineStr">
         <is>
-          <t>accx_skewness</t>
+          <t>scl_pct_95</t>
         </is>
       </c>
       <c r="B103" t="n">
-        <v>0.4376713213249896</v>
+        <v>0.5259474806560032</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="1" t="inlineStr">
         <is>
-          <t>scr_svd_entropy</t>
+          <t>bvp_kurtosis</t>
         </is>
       </c>
       <c r="B104" t="n">
-        <v>0.4540467955452093</v>
+        <v>0.5259464336196396</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="1" t="inlineStr">
         <is>
-          <t>scr_entropy</t>
+          <t>hrv_skewness</t>
         </is>
       </c>
       <c r="B105" t="n">
-        <v>0.4540467955452093</v>
+        <v>0.527960408064972</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="1" t="inlineStr">
         <is>
-          <t>accx_pct_5</t>
+          <t>accy_n_below_mean</t>
         </is>
       </c>
       <c r="B106" t="n">
-        <v>0.4660002861899394</v>
+        <v>0.5326940594646852</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="1" t="inlineStr">
         <is>
-          <t>hrv_std</t>
+          <t>accx_skewness</t>
         </is>
       </c>
       <c r="B107" t="n">
-        <v>0.4675795660383285</v>
+        <v>0.5312336182435616</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="1" t="inlineStr">
         <is>
-          <t>scl_min</t>
+          <t>bvp_svd_entropy</t>
         </is>
       </c>
       <c r="B108" t="n">
-        <v>0.4662754822474985</v>
+        <v>0.5367595271583783</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="1" t="inlineStr">
         <is>
-          <t>scr_max</t>
+          <t>accx_perm_entropy</t>
         </is>
       </c>
       <c r="B109" t="n">
-        <v>0.4643053088233754</v>
+        <v>0.5734185388258535</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="1" t="inlineStr">
         <is>
-          <t>scl_mean</t>
+          <t>accy_ptp</t>
         </is>
       </c>
       <c r="B110" t="n">
-        <v>0.463202430520412</v>
+        <v>0.5799368637072766</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="1" t="inlineStr">
         <is>
-          <t>accy_n_sign_changes</t>
+          <t>bvp_peaks</t>
         </is>
       </c>
       <c r="B111" t="n">
-        <v>0.4448546888033422</v>
+        <v>0.6041045570512664</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="1" t="inlineStr">
         <is>
-          <t>scr_perm_entropy</t>
+          <t>hrv_perm_entropy</t>
         </is>
       </c>
       <c r="B112" t="n">
-        <v>0.4448546888033422</v>
+        <v>0.6054065467693693</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="1" t="inlineStr">
         <is>
-          <t>hrv_perm_entropy</t>
+          <t>accx_n_above_mean</t>
         </is>
       </c>
       <c r="B113" t="n">
-        <v>0.4448546888033422</v>
+        <v>0.5970691707122988</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_below_mean</t>
+          <t>scl_pct_5</t>
         </is>
       </c>
       <c r="B114" t="n">
-        <v>0.4396456828945669</v>
+        <v>0.6045704882330564</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="1" t="inlineStr">
         <is>
-          <t>accy_iqr</t>
+          <t>accz_sum</t>
         </is>
       </c>
       <c r="B115" t="n">
-        <v>0.4893088861976176</v>
+        <v>0.514313685114284</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="1" t="inlineStr">
         <is>
-          <t>bvp_min</t>
+          <t>bvp_std</t>
         </is>
       </c>
       <c r="B116" t="n">
-        <v>0.4902157941945324</v>
+        <v>0.5188482250988576</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="1" t="inlineStr">
         <is>
-          <t>accx_svd_entropy</t>
+          <t>scl_iqr_5_95</t>
         </is>
       </c>
       <c r="B117" t="n">
-        <v>0.4820473400041184</v>
+        <v>0.5097634395842567</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="1" t="inlineStr">
         <is>
-          <t>accz_std</t>
+          <t>accy_pct_5</t>
         </is>
       </c>
       <c r="B118" t="n">
-        <v>0.474785793810619</v>
+        <v>0.5108277520478286</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="1" t="inlineStr">
         <is>
-          <t>accy_energy</t>
+          <t>accz_std</t>
         </is>
       </c>
       <c r="B119" t="n">
-        <v>0.4812165166496233</v>
+        <v>0.5102710777145291</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="1" t="inlineStr">
         <is>
-          <t>scl_std</t>
+          <t>scr_pct_5</t>
         </is>
       </c>
       <c r="B120" t="n">
-        <v>0.4818471815526153</v>
+        <v>0.5096393657751734</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="1" t="inlineStr">
         <is>
-          <t>scr_skewness</t>
+          <t>hrv_n_below_mean</t>
         </is>
       </c>
       <c r="B121" t="n">
-        <v>0.4818471815526153</v>
+        <v>0.5088095894570418</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="1" t="inlineStr">
         <is>
-          <t>scr_peaks</t>
+          <t>accy_min</t>
         </is>
       </c>
       <c r="B122" t="n">
-        <v>0.4829125410525507</v>
+        <v>0.5080194260146655</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="1" t="inlineStr">
         <is>
-          <t>accx_energy</t>
+          <t>scr_rms</t>
         </is>
       </c>
       <c r="B123" t="n">
-        <v>0.4895423753066944</v>
+        <v>0.5062827416996192</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="1" t="inlineStr">
         <is>
-          <t>accx_iqr</t>
+          <t>bvp_min</t>
         </is>
       </c>
       <c r="B124" t="n">
-        <v>0.484293756522164</v>
+        <v>0.5063213075390108</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="1" t="inlineStr">
         <is>
-          <t>bvp_rms</t>
+          <t>scl_svd_entropy</t>
         </is>
       </c>
       <c r="B125" t="n">
-        <v>0.4768748058620076</v>
+        <v>0.4994506549212454</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="1" t="inlineStr">
         <is>
-          <t>accz_kurtosis</t>
+          <t>accy_skewness</t>
         </is>
       </c>
       <c r="B126" t="n">
-        <v>0.4768748058620076</v>
+        <v>0.501266564987802</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_above_mean</t>
+          <t>accy_pct_95</t>
         </is>
       </c>
       <c r="B127" t="n">
-        <v>0.4768748058620076</v>
+        <v>0.4900261061066651</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="1" t="inlineStr">
         <is>
-          <t>accx_rms</t>
+          <t>scr_max</t>
         </is>
       </c>
       <c r="B128" t="n">
-        <v>0.4739153575803688</v>
+        <v>0.4973689721244019</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="1" t="inlineStr">
         <is>
-          <t>scr_pct_95</t>
+          <t>accx_pct_5</t>
         </is>
       </c>
       <c r="B129" t="n">
-        <v>0.4779015995225515</v>
+        <v>0.4828542560283118</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="1" t="inlineStr">
         <is>
-          <t>accz_perm_entropy</t>
+          <t>accy_iqr_5_95</t>
         </is>
       </c>
       <c r="B130" t="n">
-        <v>0.4829532009646695</v>
+        <v>0.502851080018009</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="1" t="inlineStr">
         <is>
-          <t>accx_entropy</t>
+          <t>accz_energy</t>
         </is>
       </c>
       <c r="B131" t="n">
-        <v>0.4807432562132883</v>
+        <v>0.502413244311975</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="1" t="inlineStr">
         <is>
-          <t>scr_kurtosis</t>
+          <t>accy_kurtosis</t>
         </is>
       </c>
       <c r="B132" t="n">
-        <v>0.4796382838375977</v>
+        <v>0.5043083801300419</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="1" t="inlineStr">
         <is>
-          <t>hrv_ptp</t>
+          <t>scl_std</t>
         </is>
       </c>
       <c r="B133" t="n">
-        <v>0.4747055210227451</v>
+        <v>0.4994496078848819</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="1" t="inlineStr">
         <is>
-          <t>scr_lineintegral</t>
+          <t>scl_sum</t>
         </is>
       </c>
       <c r="B134" t="n">
-        <v>0.4724955762713639</v>
+        <v>0.4992129776667144</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="1" t="inlineStr">
         <is>
-          <t>scl_entropy</t>
+          <t>scr_entropy</t>
         </is>
       </c>
       <c r="B135" t="n">
-        <v>0.4812165166496233</v>
+        <v>0.4992129776667144</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="1" t="inlineStr">
         <is>
-          <t>scl_n_above_mean</t>
+          <t>hrv_n_above_mean</t>
         </is>
       </c>
       <c r="B136" t="n">
-        <v>0.4820452459313912</v>
+        <v>0.4992129776667144</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="1" t="inlineStr">
         <is>
-          <t>accx_lineintegral</t>
+          <t>scr_energy</t>
         </is>
       </c>
       <c r="B137" t="n">
-        <v>0.4837027044949271</v>
+        <v>0.4987397172303794</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="1" t="inlineStr">
         <is>
-          <t>accy_perm_entropy</t>
+          <t>scl_kurtosis</t>
         </is>
       </c>
       <c r="B138" t="n">
-        <v>0.4941217633488411</v>
+        <v>0.4993318162939799</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" s="1" t="inlineStr">
         <is>
-          <t>accy_peaks</t>
+          <t>bvp_iqr</t>
         </is>
       </c>
       <c r="B139" t="n">
-        <v>0.4941217633488411</v>
+        <v>0.4983842483849464</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="1" t="inlineStr">
         <is>
-          <t>accz_n_below_mean</t>
+          <t>bvp_n_below_mean</t>
         </is>
       </c>
       <c r="B140" t="n">
-        <v>0.4948316540033436</v>
+        <v>0.4985020399758484</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" s="1" t="inlineStr">
         <is>
-          <t>scl_pct_5</t>
+          <t>accx_min</t>
         </is>
       </c>
       <c r="B141" t="n">
-        <v>0.4947524282518332</v>
+        <v>0.4962535293850756</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" s="1" t="inlineStr">
         <is>
-          <t>scr_n_sign_changes</t>
+          <t>accy_sum</t>
         </is>
       </c>
       <c r="B142" t="n">
-        <v>0.4947524282518332</v>
+        <v>0.4998082178394056</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" s="1" t="inlineStr">
         <is>
-          <t>accx_n_sign_changes</t>
+          <t>accz_n_above_mean</t>
         </is>
       </c>
       <c r="B143" t="n">
-        <v>0.4955811575336012</v>
+        <v>0.4984634741364568</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" s="1" t="inlineStr">
         <is>
-          <t>hrv_iqr_5_95</t>
+          <t>scl_n_below_mean</t>
         </is>
       </c>
       <c r="B144" t="n">
-        <v>0.49337121278222</v>
+        <v>0.5003586099545237</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" s="1" t="inlineStr">
         <is>
-          <t>accx_sum</t>
+          <t>scr_min</t>
         </is>
       </c>
       <c r="B145" t="n">
-        <v>0.4887543059370452</v>
+        <v>0.5003586099545237</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" s="1" t="inlineStr">
         <is>
-          <t>accz_iqr_5_95</t>
+          <t>bvp_rms</t>
         </is>
       </c>
       <c r="B146" t="n">
-        <v>0.4986980102818971</v>
+        <v>0.4972000502577454</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_above_mean</t>
+          <t>accx_n_below_mean</t>
         </is>
       </c>
       <c r="B147" t="n">
-        <v>0.5</v>
+        <v>0.4967257427850469</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" s="1" t="inlineStr">
         <is>
-          <t>scr_rms</t>
+          <t>accx_svd_entropy</t>
         </is>
       </c>
       <c r="B148" t="n">
-        <v>0.5</v>
+        <v>0.4975159062274233</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" s="1" t="inlineStr">
         <is>
-          <t>accz_pct_95</t>
+          <t>scr_skewness</t>
         </is>
       </c>
       <c r="B149" t="n">
-        <v>0.5</v>
+        <v>0.4973970676001578</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" s="1" t="inlineStr">
         <is>
-          <t>accz_n_above_mean</t>
+          <t>accx_max</t>
         </is>
       </c>
       <c r="B150" t="n">
-        <v>0.5</v>
+        <v>0.4975544720668149</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" s="1" t="inlineStr">
         <is>
-          <t>accx_min</t>
+          <t>accy_std</t>
         </is>
       </c>
       <c r="B151" t="n">
-        <v>0.5</v>
+        <v>0.4985009929394848</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" s="1" t="inlineStr">
         <is>
-          <t>accy_kurtosis</t>
+          <t>bvp_pct_95</t>
         </is>
       </c>
       <c r="B152" t="n">
-        <v>0.5</v>
+        <v>0.4996059653151754</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" s="1" t="inlineStr">
         <is>
-          <t>bvp_peaks</t>
+          <t>scl_mean</t>
         </is>
       </c>
       <c r="B153" t="n">
-        <v>0.5</v>
+        <v>0.499526739563665</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" s="1" t="inlineStr">
         <is>
-          <t>accz_skewness</t>
+          <t>accz_n_sign_changes</t>
         </is>
       </c>
       <c r="B154" t="n">
-        <v>0.5</v>
+        <v>0.499526739563665</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" s="1" t="inlineStr">
         <is>
-          <t>accy_svd_entropy</t>
+          <t>bvp_entropy</t>
         </is>
       </c>
       <c r="B155" t="n">
-        <v>0.5</v>
+        <v>0.499526739563665</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" s="1" t="inlineStr">
         <is>
-          <t>accz_rms</t>
+          <t>scl_n_sign_changes</t>
         </is>
       </c>
       <c r="B156" t="n">
-        <v>0.5</v>
+        <v>0.499526739563665</v>
       </c>
     </row>
   </sheetData>
